--- a/nmtcapp/templates/pipeline_template.xlsx
+++ b/nmtcapp/templates/pipeline_template.xlsx
@@ -696,7 +696,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CDE Profile — NMTC Application Builder v1.1</t>
+          <t>CDE Profile — NMTC Application Builder v1.1  |  BLANK TEMPLATE: enter your own CDE's details in row 4</t>
         </is>
       </c>
     </row>
@@ -880,128 +880,36 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Riverbend Community Capital CDE, LLC</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>CDE-2018-0117</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>82-1234567</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>2018-06-20</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Deploy NMTC capital into deep-distress communities across the Midwest and South.</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>https://riverbendcommunitycapital.org</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>nonprofit</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>IL,OH,MI,IN,TN,GA,LA,MO</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>CY2025</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="M4" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O4" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P4" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q4" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R4" s="10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S4" s="10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="T4" s="10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="U4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="X4" s="10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Y4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Z4" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA4" s="10" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AB4" s="10" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AC4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AD4" s="8" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="8" t="n"/>
+      <c r="P4" s="8" t="n"/>
+      <c r="Q4" s="8" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="8" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="8" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="8" t="n"/>
+      <c r="AD4" s="8" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1012,40 +920,40 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="L2:S2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A5:O5"/>
     <mergeCell ref="A1:AD1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="L2:S2"/>
-    <mergeCell ref="T2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A5:O5"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="O4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="O4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="V4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="V4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="W4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="W4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="Y4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="Y4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="AD4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AD4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AC4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N,Unknown"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"AL,AK,AZ,AR,CA,CO,CT,DE,FL,GA,HI,ID,IL,IN,IA,KS,KY,LA,ME,MD,MA,MI,MN,MS,MO,MT,NE,NV,NH,NJ,NM,NY,NC,ND,OH,OK,OR,PA,RI,SC,SD,TN,TX,UT,VT,VA,WA,WV,WI,WY,DC,PR,GU,VI,AS,MP"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"nonprofit,for_profit,government"</formula1>
     </dataValidation>
-    <dataValidation sqref="K4" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="K4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"CY2025,CY2026"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1095,7 +1003,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>Pipeline — NMTC Application Builder v1.1  |  One row per project</t>
+          <t>Pipeline — NMTC Application Builder v1.1  |  BLANK TEMPLATE: one row per project, starting at row 4</t>
         </is>
       </c>
     </row>
@@ -1289,676 +1197,208 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>PRJ-001</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Southside Community Health Center</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Southside HC QALICB LLC</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>3400 S Michigan Ave</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K4" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>18</v>
-      </c>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
-      <c r="N4" s="8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="O4" s="21" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q4" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R4" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S4" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T4" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U4" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V4" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t>17031838200</t>
-        </is>
-      </c>
-      <c r="Y4" s="8" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="Z4" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA4" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="N4" s="8" t="n"/>
+      <c r="O4" s="21" t="n"/>
+      <c r="P4" s="21" t="n"/>
+      <c r="Q4" s="21" t="n"/>
+      <c r="R4" s="21" t="n"/>
+      <c r="S4" s="21" t="n"/>
+      <c r="T4" s="22" t="n"/>
+      <c r="U4" s="22" t="n"/>
+      <c r="V4" s="21" t="n"/>
+      <c r="W4" s="8" t="n"/>
+      <c r="X4" s="8" t="n"/>
+      <c r="Y4" s="8" t="n"/>
+      <c r="Z4" s="23" t="n"/>
+      <c r="AA4" s="23" t="n"/>
       <c r="AB4" s="23" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>PRJ-002</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>East Houston Charter Academy</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>East Houston Academy QALICB LLC</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>5200 Lawndale St</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Houston</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>education</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n"/>
-      <c r="O5" s="21" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q5" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S5" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T5" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U5" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V5" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t>48201223400</t>
-        </is>
-      </c>
-      <c r="Y5" s="8" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="Z5" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA5" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="O5" s="21" t="n"/>
+      <c r="P5" s="21" t="n"/>
+      <c r="Q5" s="21" t="n"/>
+      <c r="R5" s="21" t="n"/>
+      <c r="S5" s="21" t="n"/>
+      <c r="T5" s="22" t="n"/>
+      <c r="U5" s="22" t="n"/>
+      <c r="V5" s="21" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="n"/>
+      <c r="Y5" s="8" t="n"/>
+      <c r="Z5" s="23" t="n"/>
+      <c r="AA5" s="23" t="n"/>
       <c r="AB5" s="23" t="n"/>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>PRJ-003</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Bronx Food Hub</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Bronx Food Hub QALICB LLC</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>800 Hunts Point Ave</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Bronx</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>small_business</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>8</v>
-      </c>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="O6" s="21" t="inlineStr">
-        <is>
-          <t>severe</t>
-        </is>
-      </c>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q6" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R6" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S6" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="T6" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U6" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V6" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="X6" s="8" t="inlineStr">
-        <is>
-          <t>36005035900</t>
-        </is>
-      </c>
-      <c r="Y6" s="8" t="inlineStr">
-        <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z6" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA6" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="N6" s="8" t="n"/>
+      <c r="O6" s="21" t="n"/>
+      <c r="P6" s="21" t="n"/>
+      <c r="Q6" s="21" t="n"/>
+      <c r="R6" s="21" t="n"/>
+      <c r="S6" s="21" t="n"/>
+      <c r="T6" s="22" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="21" t="n"/>
+      <c r="W6" s="8" t="n"/>
+      <c r="X6" s="8" t="n"/>
+      <c r="Y6" s="8" t="n"/>
+      <c r="Z6" s="23" t="n"/>
+      <c r="AA6" s="23" t="n"/>
       <c r="AB6" s="23" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>PRJ-014</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Phoenix Native American Health Clinic</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Phoenix Native HC QALICB LLC</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>4212 W Indian School Rd</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>healthcare</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="L7" s="8" t="n">
-        <v>25</v>
-      </c>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
       <c r="M7" s="8" t="n"/>
-      <c r="N7" s="8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="P7" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q7" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="R7" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S7" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T7" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U7" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V7" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W7" s="8" t="inlineStr">
-        <is>
-          <t>urban</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t>04013118400</t>
-        </is>
-      </c>
-      <c r="Y7" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="Z7" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA7" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="21" t="n"/>
+      <c r="P7" s="21" t="n"/>
+      <c r="Q7" s="21" t="n"/>
+      <c r="R7" s="21" t="n"/>
+      <c r="S7" s="21" t="n"/>
+      <c r="T7" s="22" t="n"/>
+      <c r="U7" s="22" t="n"/>
+      <c r="V7" s="21" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="n"/>
+      <c r="Y7" s="8" t="n"/>
+      <c r="Z7" s="23" t="n"/>
+      <c r="AA7" s="23" t="n"/>
       <c r="AB7" s="23" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>PRJ-017</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Rural Mississippi Health Access Center</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Rural MS Health QALICB LLC</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>510 Main St</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Greenville</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>MS</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>healthcare</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>real_estate</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n">
-        <v>8000</v>
-      </c>
-      <c r="O8" s="21" t="inlineStr">
-        <is>
-          <t>deep</t>
-        </is>
-      </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q8" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="S8" s="21" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="T8" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="U8" s="22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="V8" s="21" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t>rural</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t>28065950100</t>
-        </is>
-      </c>
-      <c r="Y8" s="8" t="inlineStr">
-        <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="Z8" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA8" s="23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="N8" s="8" t="n"/>
+      <c r="O8" s="21" t="n"/>
+      <c r="P8" s="21" t="n"/>
+      <c r="Q8" s="21" t="n"/>
+      <c r="R8" s="21" t="n"/>
+      <c r="S8" s="21" t="n"/>
+      <c r="T8" s="22" t="n"/>
+      <c r="U8" s="22" t="n"/>
+      <c r="V8" s="21" t="n"/>
+      <c r="W8" s="8" t="n"/>
+      <c r="X8" s="8" t="n"/>
+      <c r="Y8" s="8" t="n"/>
+      <c r="Z8" s="23" t="n"/>
+      <c r="AA8" s="23" t="n"/>
       <c r="AB8" s="23" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="T2:U2"/>
     <mergeCell ref="A1:AB1"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="K2:N2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="Z2:AB2"/>
   </mergeCells>
   <dataValidations count="14">
-    <dataValidation sqref="P4:P1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="P4:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q4:Q1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="Q4:Q1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="R4:R1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="R4:R1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="S4:S1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="S4:S1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="T4:T1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="T4:T1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="U4:U1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="U4:U1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="V4:V1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="V4:V1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="Z4:Z1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="Z4:Z1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="AA4:AA1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="AA4:AA1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"AL,AK,AZ,AR,CA,CO,CT,DE,FL,GA,HI,ID,IL,IN,IA,KS,KY,LA,ME,MD,MA,MI,MN,MS,MO,MT,NE,NV,NH,NJ,NM,NY,NC,ND,OH,OK,OR,PA,RI,SC,SD,TN,TX,UT,VT,VA,WA,WV,WI,WY,DC,PR,GU,VI,AS,MP"</formula1>
     </dataValidation>
-    <dataValidation sqref="G4:G1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G4:G1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"healthcare,affordable_housing,education,small_business,mixed_use,community_facility,clean_energy,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="H4:H1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="H4:H1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"real_estate,operating_business,mixed_use"</formula1>
     </dataValidation>
-    <dataValidation sqref="O4:O1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="O4:O1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"deep,severe,lic,ineligible"</formula1>
     </dataValidation>
-    <dataValidation sqref="W4:W1000" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="W4:W1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"urban,rural,suburban"</formula1>
     </dataValidation>
   </dataValidations>

--- a/nmtcapp/templates/pipeline_template.xlsx
+++ b/nmtcapp/templates/pipeline_template.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -293,6 +293,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,6 +709,11 @@
           <t>Identity</t>
         </is>
       </c>
+      <c r="J2" s="32" t="inlineStr">
+        <is>
+          <t>Application Request</t>
+        </is>
+      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Business Strategy</t>
@@ -919,12 +927,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="T2:Y2"/>
     <mergeCell ref="L2:S2"/>
     <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A5:O5"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
@@ -954,7 +963,7 @@
       <formula1>"nonprofit,for_profit,government"</formula1>
     </dataValidation>
     <dataValidation sqref="K4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>"CY2025,CY2026"</formula1>
+      <formula1>"CY2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1969,7 +1978,7 @@
       </c>
       <c r="H2" s="31" t="inlineStr">
         <is>
-          <t>CY2025</t>
+          <t>CY2026</t>
         </is>
       </c>
     </row>
@@ -2007,11 +2016,6 @@
       <c r="G3" s="31" t="inlineStr">
         <is>
           <t>for_profit</t>
-        </is>
-      </c>
-      <c r="H3" s="31" t="inlineStr">
-        <is>
-          <t>CY2026</t>
         </is>
       </c>
     </row>

--- a/nmtcapp/templates/pipeline_template.xlsx
+++ b/nmtcapp/templates/pipeline_template.xlsx
@@ -200,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -296,6 +296,8 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -661,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -694,12 +696,16 @@
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="30" customWidth="1" min="32" max="32"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="26" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CDE Profile — NMTC Application Builder v1.1  |  BLANK TEMPLATE: enter your own CDE's details in row 4</t>
+          <t>CDE Profile — NMTC Application Builder v1.2  |  BLANK TEMPLATE: enter your own CDE's details in row 4</t>
         </is>
       </c>
     </row>
@@ -734,6 +740,11 @@
           <t>Phase 2</t>
         </is>
       </c>
+      <c r="AE2" s="5" t="inlineStr">
+        <is>
+          <t>Contact &amp; Governance</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -884,6 +895,26 @@
       <c r="AD3" s="7" t="inlineStr">
         <is>
           <t>Prior Reporting Issues (Y/N)</t>
+        </is>
+      </c>
+      <c r="AE3" s="7" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="AF3" s="7" t="inlineStr">
+        <is>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="AG3" s="7" t="inlineStr">
+        <is>
+          <t>Board Members</t>
+        </is>
+      </c>
+      <c r="AH3" s="7" t="inlineStr">
+        <is>
+          <t>Community Representatives</t>
         </is>
       </c>
     </row>
@@ -918,6 +949,10 @@
       <c r="AB4" s="10" t="n"/>
       <c r="AC4" s="8" t="n"/>
       <c r="AD4" s="8" t="n"/>
+      <c r="AE4" s="8" t="n"/>
+      <c r="AF4" s="8" t="n"/>
+      <c r="AG4" s="8" t="n"/>
+      <c r="AH4" s="8" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -927,15 +962,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="Z2:AB2"/>
     <mergeCell ref="T2:Y2"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="L2:S2"/>
+    <mergeCell ref="J2:K2"/>
     <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="J2:K2"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="AE2:AH2"/>
   </mergeCells>
   <dataValidations count="9">
     <dataValidation sqref="O4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
@@ -1360,8 +1396,8 @@
   <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="O2:S2"/>
     <mergeCell ref="W2:X2"/>
-    <mergeCell ref="O2:S2"/>
     <mergeCell ref="T2:U2"/>
     <mergeCell ref="A1:AB1"/>
     <mergeCell ref="G2:J2"/>
@@ -1421,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1430,7 +1466,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="24" t="inlineStr">
         <is>
-          <t>NMTC APPLICATION BUILDER — TEMPLATE v1.1 INSTRUCTIONS</t>
+          <t>NMTC APPLICATION BUILDER — TEMPLATE v1.2 INSTRUCTIONS</t>
         </is>
       </c>
     </row>
@@ -1871,6 +1907,55 @@
       <c r="A69" s="27" t="inlineStr">
         <is>
           <t>sub-criteria. Treat all scores as directional, not authoritative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="33" t="inlineStr">
+        <is>
+          <t>NEW IN v1.2 — CONTACT &amp; GOVERNANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>'contact' and 'governance' are two of the eight fields a CDE profile requires, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>through v1.1 this sheet collected NEITHER — so a profile built from this workbook could</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>never be complete. Four columns now supply them:</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Contact Name, Contact Email            → contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Board Members, Community Representatives → governance</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>A v1.1 workbook still loads. It simply supplies neither field, exactly as before.</t>
         </is>
       </c>
     </row>
